--- a/tamu_data/evals/golden_sets/smoke_v1.xlsx
+++ b/tamu_data/evals/golden_sets/smoke_v1.xlsx
@@ -452,7 +452,6 @@
           <t>tell me about CSCE 638</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>metadata_default</t>
@@ -468,7 +467,6 @@
           <t>what should I take alongside CSCE 638?</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>recurrent_default</t>
@@ -484,7 +482,6 @@
           <t>compare CSCE 638 and CSCE 670</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>metadata_default</t>
